--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 09:13</t>
+          <t>更新时间: 2026-09-14 09:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 09:15</t>
+          <t>更新时间: 2026-09-15 09:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 09:17</t>
+          <t>更新时间: 2026-09-16 09:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 09:14</t>
+          <t>更新时间: 2026-09-17 09:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 09:15</t>
+          <t>更新时间: 2026-09-18 09:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 09:14</t>
+          <t>更新时间: 2026-09-19 09:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 09:13</t>
+          <t>更新时间: 2026-09-20 09:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 09:13</t>
+          <t>更新时间: 2026-09-21 09:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 09:14</t>
+          <t>更新时间: 2026-09-22 09:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 09:13</t>
+          <t>更新时间: 2026-09-23 09:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 09:14</t>
+          <t>更新时间: 2026-09-24 09:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 09:16</t>
+          <t>更新时间: 2026-09-25 09:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 09:14</t>
+          <t>更新时间: 2026-09-26 09:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 09:13</t>
+          <t>更新时间: 2026-09-27 09:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 09:14</t>
+          <t>更新时间: 2026-09-28 09:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 09:16</t>
+          <t>更新时间: 2026-09-29 09:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 09:16</t>
+          <t>更新时间: 2026-09-30 09:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 09:17</t>
+          <t>更新时间: 2026-10-01 09:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 09:18</t>
+          <t>更新时间: 2026-10-02 09:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 09:17</t>
+          <t>更新时间: 2026-10-03 09:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 09:15</t>
+          <t>更新时间: 2026-10-04 12:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 12:02</t>
+          <t>更新时间: 2026-10-05 14:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 14:44</t>
+          <t>更新时间: 2026-10-06 15:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 15:23</t>
+          <t>更新时间: 2026-10-07 15:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 15:02</t>
+          <t>更新时间: 2026-10-08 15:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 15:11</t>
+          <t>更新时间: 2026-10-09 15:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 15:15</t>
+          <t>更新时间: 2026-10-10 14:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 14:53</t>
+          <t>更新时间: 2026-10-11 14:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 14:57</t>
+          <t>更新时间: 2026-10-12 15:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 15:10</t>
+          <t>更新时间: 2026-10-13 15:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 15:33</t>
+          <t>更新时间: 2026-10-14 13:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 13:58</t>
+          <t>更新时间: 2026-10-15 13:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-15 13:44</t>
+          <t>更新时间: 2026-10-16 13:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-16 13:40</t>
+          <t>更新时间: 2026-10-17 13:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-17 13:26</t>
+          <t>更新时间: 2026-10-18 13:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-18 13:37</t>
+          <t>更新时间: 2026-10-19 13:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-19 13:55</t>
+          <t>更新时间: 2026-10-20 13:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-20 13:47</t>
+          <t>更新时间: 2026-10-21 13:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-21 13:51</t>
+          <t>更新时间: 2026-10-22 13:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-22 13:54</t>
+          <t>更新时间: 2026-10-23 13:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-23 13:52</t>
+          <t>更新时间: 2026-10-24 13:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-24 13:35</t>
+          <t>更新时间: 2026-10-25 13:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-25 13:50</t>
+          <t>更新时间: 2026-10-26 13:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-26 13:53</t>
+          <t>更新时间: 2026-10-27 14:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-27 14:06</t>
+          <t>更新时间: 2026-10-28 14:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-28 14:44</t>
+          <t>更新时间: 2026-10-29 14:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-29 14:52</t>
+          <t>更新时间: 2026-10-30 14:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-30 14:55</t>
+          <t>更新时间: 2026-10-31 14:49</t>
         </is>
       </c>
     </row>
